--- a/resources/templates/contract/智书合同字段-主播流程.xlsx
+++ b/resources/templates/contract/智书合同字段-主播流程.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="188">
   <si>
     <t>contract_number（合同编码）</t>
   </si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t>custom_1024_61820798c0f348658d8daa64f8b2aef9（主播卡片）</t>
+  </si>
+  <si>
+    <t>泛微主播卡片ID</t>
   </si>
   <si>
     <t>custom_1_ab6f99ee02e549469ec5b2d4a5a98452（主播姓名）</t>
@@ -619,7 +622,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -636,6 +639,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1148,152 +1158,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1308,6 +1318,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1629,14 +1642,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BA1"/>
+  <dimension ref="A1:BB1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.2857142857143" customWidth="1"/>
-    <col min="2" max="53" width="34" customWidth="1"/>
+    <col min="2" max="54" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1" spans="1:53">
+    <row r="1" ht="60" customHeight="1" spans="1:54">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1712,7 +1725,7 @@
       <c r="Y1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
       <c r="AA1" s="5" t="s">
@@ -1730,7 +1743,7 @@
       <c r="AE1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="5" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="3" t="s">
@@ -1763,13 +1776,13 @@
       <c r="AP1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="5" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AR1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AS1" s="5" t="s">
         <v>44</v>
       </c>
       <c r="AT1" s="3" t="s">
@@ -1778,7 +1791,7 @@
       <c r="AU1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="5" t="s">
+      <c r="AV1" s="3" t="s">
         <v>47</v>
       </c>
       <c r="AW1" s="5" t="s">
@@ -1787,14 +1800,17 @@
       <c r="AX1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="3" t="s">
+      <c r="AY1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="5" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="3" t="s">
+      <c r="BA1" s="5" t="s">
         <v>52</v>
+      </c>
+      <c r="BB1" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1811,19 +1827,19 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1048576">
       <formula1>DV_4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AE2:AE1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF2:AF1048576">
       <formula1>DV_8</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF2:AF1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AG2:AG1048576">
       <formula1>DV_5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AS2:AS1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AT2:AT1048576">
       <formula1>DV_6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AT2:AT1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AU2:AU1048576">
       <formula1>DV_7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AY2:AY1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AZ2:AZ1048576">
       <formula1>DV_9</formula1>
     </dataValidation>
   </dataValidations>
@@ -1840,498 +1856,498 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="G5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="G6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="G7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="G8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="G9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="G10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="G11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="G12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="G13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="G14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="G15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="G16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="7:9">
       <c r="G17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="7:9">
       <c r="G18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="7:9">
       <c r="H19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I19" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="7:9">
       <c r="H20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="7:9">
       <c r="H21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="7:9">
       <c r="H22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="7:9">
       <c r="H23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I23" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="7:9">
       <c r="H24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="7:9">
       <c r="H25" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="7:9">
       <c r="H26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="7:9">
       <c r="H27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I27" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="7:9">
       <c r="H28" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="7:9">
       <c r="H29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="7:9">
       <c r="H30" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I30" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="7:9">
       <c r="H31" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="7:9">
       <c r="H32" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="8:8">
       <c r="H33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="34" spans="8:8">
       <c r="H34" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="8:8">
       <c r="H35" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="36" spans="8:8">
       <c r="H36" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="8:8">
       <c r="H37" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38" spans="8:8">
       <c r="H38" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="8:8">
       <c r="H39" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="8:8">
       <c r="H40" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" spans="8:8">
       <c r="H41" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="8:8">
       <c r="H42" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="8:8">
       <c r="H43" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="44" spans="8:8">
       <c r="H44" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" spans="8:8">
       <c r="H45" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" spans="8:8">
       <c r="H46" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="8:8">
       <c r="H47" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="8:8">
       <c r="H48" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" spans="8:8">
       <c r="H49" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" spans="8:8">
       <c r="H50" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" spans="8:8">
       <c r="H51" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="52" spans="8:8">
       <c r="H52" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53" spans="8:8">
       <c r="H53" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="54" spans="8:8">
       <c r="H54" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="55" spans="8:8">
       <c r="H55" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="56" spans="8:8">
       <c r="H56" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2354,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -2377,7 +2393,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -2401,16 +2417,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -2439,7 +2455,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2463,7 +2479,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
